--- a/Results/rbf_fd_parameter_study_8.xlsx
+++ b/Results/rbf_fd_parameter_study_8.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1053,6 +1053,721 @@
         <v>250</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D12" t="n">
+        <v>100</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>801.0799520740145</v>
+      </c>
+      <c r="L12" t="n">
+        <v>532.4815275657328</v>
+      </c>
+      <c r="M12" t="n">
+        <v>636.8736544731679</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.1418531083605381</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.02131295313565971</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>100</v>
+      </c>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2209.949145373786</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1338.671761395286</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1561.917120285973</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.1424000606224828</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.02140422650767193</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>100</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>100</v>
+      </c>
+      <c r="E14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.005008560905401489</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.003588168178376403</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.01256710024106528</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.01011738947301047</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.003658962142049161</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>100</v>
+      </c>
+      <c r="B15" t="n">
+        <v>100</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>100</v>
+      </c>
+      <c r="E15" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H15" t="n">
+        <v>12</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.0001003280891885995</v>
+      </c>
+      <c r="L15" t="n">
+        <v>6.574582458716447e-05</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.000231816066847103</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.0005722029614131511</v>
+      </c>
+      <c r="O15" t="n">
+        <v>9.339228826142352e-05</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>100</v>
+      </c>
+      <c r="B16" t="n">
+        <v>100</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>100</v>
+      </c>
+      <c r="E16" t="n">
+        <v>10</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H16" t="n">
+        <v>12</v>
+      </c>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="b">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.005206400887190266</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.003036862421478096</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.009683364544926713</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.0007785110764659702</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.0002913998058493125</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>100</v>
+      </c>
+      <c r="B17" t="n">
+        <v>100</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>100</v>
+      </c>
+      <c r="E17" t="n">
+        <v>10</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H17" t="n">
+        <v>12</v>
+      </c>
+      <c r="I17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.0006868713526972873</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.0004739365250237022</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.003310424782954531</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.0004160031730840515</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.0002519014388082528</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>100</v>
+      </c>
+      <c r="B18" t="n">
+        <v>100</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>100</v>
+      </c>
+      <c r="E18" t="n">
+        <v>10</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H18" t="n">
+        <v>12</v>
+      </c>
+      <c r="I18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" t="b">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.0004182009467934709</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.0003363376131591185</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.001868819840252789</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.0008000998633794607</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.0005785670172972821</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>100</v>
+      </c>
+      <c r="B19" t="n">
+        <v>100</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D19" t="n">
+        <v>100</v>
+      </c>
+      <c r="E19" t="n">
+        <v>10</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H19" t="n">
+        <v>12</v>
+      </c>
+      <c r="I19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" t="b">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.0004534944972619437</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.0004229437521206131</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.001315144475988922</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.0008732732325546684</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.001041750193455918</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>100</v>
+      </c>
+      <c r="B20" t="n">
+        <v>100</v>
+      </c>
+      <c r="C20" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" t="n">
+        <v>100</v>
+      </c>
+      <c r="E20" t="n">
+        <v>10</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H20" t="n">
+        <v>12</v>
+      </c>
+      <c r="I20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20" t="b">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.300498200782122e-05</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.135257818445861e-05</v>
+      </c>
+      <c r="M20" t="n">
+        <v>5.520072525578142e-05</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.0001220463173009183</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3.234251481621363e-05</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>100</v>
+      </c>
+      <c r="B21" t="n">
+        <v>100</v>
+      </c>
+      <c r="C21" t="n">
+        <v>5</v>
+      </c>
+      <c r="D21" t="n">
+        <v>100</v>
+      </c>
+      <c r="E21" t="n">
+        <v>10</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H21" t="n">
+        <v>12</v>
+      </c>
+      <c r="I21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21" t="b">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4.637013645771473e-05</v>
+      </c>
+      <c r="L21" t="n">
+        <v>3.279251339077064e-05</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.0002121380138445913</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.0002436074925682106</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.0001111521953009765</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>100</v>
+      </c>
+      <c r="B22" t="n">
+        <v>100</v>
+      </c>
+      <c r="C22" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D22" t="n">
+        <v>100</v>
+      </c>
+      <c r="E22" t="n">
+        <v>10</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H22" t="n">
+        <v>12</v>
+      </c>
+      <c r="I22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" t="b">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.0003518217083057252</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.0004804653251149736</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.001491463641677988</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.0009708377099184987</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.001311721561816644</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>100</v>
+      </c>
+      <c r="B23" t="n">
+        <v>100</v>
+      </c>
+      <c r="C23" t="n">
+        <v>10</v>
+      </c>
+      <c r="D23" t="n">
+        <v>100</v>
+      </c>
+      <c r="E23" t="n">
+        <v>10</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H23" t="n">
+        <v>12</v>
+      </c>
+      <c r="I23" t="b">
+        <v>0</v>
+      </c>
+      <c r="J23" t="b">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.0004200183628650664</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.0003081116829364333</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.01021681460548363</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.001796707032759248</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.0004974326288146634</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>100</v>
+      </c>
+      <c r="B24" t="n">
+        <v>100</v>
+      </c>
+      <c r="C24" t="n">
+        <v>15</v>
+      </c>
+      <c r="D24" t="n">
+        <v>100</v>
+      </c>
+      <c r="E24" t="n">
+        <v>10</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H24" t="n">
+        <v>12</v>
+      </c>
+      <c r="I24" t="b">
+        <v>0</v>
+      </c>
+      <c r="J24" t="b">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.0004796794887694945</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.0001843327600168282</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.1105444962474763</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.3369080513556885</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.02204894014522607</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Results/rbf_fd_parameter_study_8.xlsx
+++ b/Results/rbf_fd_parameter_study_8.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Stencil Nodes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1771,4 +1772,765 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.002849601053912238</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.0006354780308312859</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.004389337847906737</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.003136362864196145</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0007992132864664634</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>25</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.0003045804750017141</v>
+      </c>
+      <c r="L3" t="n">
+        <v>9.358803400746709e-05</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.001223120279006252</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.0004184934635733166</v>
+      </c>
+      <c r="O3" t="n">
+        <v>8.79150385887602e-05</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>40</v>
+      </c>
+      <c r="E4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.000199059032082172</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.000159061953190096</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.0007129935189249069</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.001041660373769317</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0002596535270132142</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>50</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.001391141214341079</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.0004987898835779875</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.004642465427682283</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.0009340249631902003</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0002669535104289256</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>65</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.0001189281858835877</v>
+      </c>
+      <c r="L6" t="n">
+        <v>9.473733160713145e-05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.0003482857133108769</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.0003362925042709412</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0002351163641455974</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>75</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.0001736303664530285</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.0001723812072925016</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.0006100760360339636</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.0005306244880896136</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0003361316033783554</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>85</v>
+      </c>
+      <c r="E8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.000169143644228213</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.000149503917536779</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.0005507263001068665</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.0006251524856121419</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0004362719124945382</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0004182009467934709</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0003363376131591185</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.001868819840252789</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.0008000998633794607</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0005785670172972821</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>115</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.0005107589678668979</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.0003518584005391032</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.001585601343766789</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.000798323372351319</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.0007416725676923301</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>130</v>
+      </c>
+      <c r="E11" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.0006636503403070126</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.0004752332098786427</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.001870730480152884</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.0008233181406588876</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.0008661134182829807</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>150</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.0005474800400640133</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.0003550520297705476</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.001291938838190524</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.0009654533541914952</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.0007790758507981971</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>200</v>
+      </c>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>7.249685725744536e-05</v>
+      </c>
+      <c r="L13" t="n">
+        <v>3.681723160669455e-05</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.0001176798069649529</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.0003131389668494087</v>
+      </c>
+      <c r="O13" t="n">
+        <v>6.646329981191174e-05</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>200</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_8.xlsx
+++ b/Results/rbf_fd_parameter_study_8.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Stencil Nodes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Center Rings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2533,4 +2534,545 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.0001455363093010923</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.0001773157710849925</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.0004953522835403382</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.0006022466822651979</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.00052706421920213</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.0006413996849286077</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.0003298633195992544</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.001465921640369833</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.0005884766876624592</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.0005486005635041719</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.9688841397736163</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.4423551236249879</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2.709104091298975</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.0006851744411297494</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0005518360201450237</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.001179654002768201</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.0006857849391908789</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.005356295489665357</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.0007134238539798344</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0005526358838132549</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>100</v>
+      </c>
+      <c r="E6" t="n">
+        <v>9</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.003559319932253612</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.002403640501117247</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.01820068418722879</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.0008052216256204681</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0005771729149687611</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>100</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.0004182009467934709</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.0003363376131591185</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.001868819840252789</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.0008000998633794607</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0005785670172972821</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>100</v>
+      </c>
+      <c r="E8" t="n">
+        <v>11</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.001806910655028694</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.001081628911736746</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.007784424566472965</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.0007991777089907866</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0005785230855149264</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0001656166118125944</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0001906695352963905</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.0005584013859588391</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.0007988780453014751</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0005779375933437105</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_8.xlsx
+++ b/Results/rbf_fd_parameter_study_8.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Stencil Nodes" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Center Rings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Eigenvalue Ratio" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3075,4 +3076,820 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.001848526080605156</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.003812495591275713</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.002634552174910064</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.0007186852271810671</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0005772251754840767</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.0005964075876117255</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.001230440808968527</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.001128417973695773</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.0006469065833350755</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.0005743229042967516</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.0003064218168248184</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0004604069447377794</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.0008189594555153749</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.000484395228477015</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0005678983152057274</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.0003412214229612485</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.000205620050157874</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.001024724370326212</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.0005511115847533524</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0005688866582045656</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>100</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.0001485166780566115</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.0001836246423338094</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.0005435345830600932</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.000718676912839876</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0005751380485776043</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>100</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.0001701389509829761</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.0001867637088638031</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.0005926507427077719</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.0007596971012486588</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0005767939785372149</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>100</v>
+      </c>
+      <c r="E8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.0003773563042487573</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.0002694973477383374</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.001285037587787244</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.0007954329812708243</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0005783552461590551</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0004182009467934709</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0003363376131591185</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.001868819840252789</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.0008000998633794607</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0005785670172972821</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>100</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.0003562832995923916</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.0002686296967311915</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.001347468651448333</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.0008038712833952428</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.0005787392116207714</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>100</v>
+      </c>
+      <c r="E11" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.0003653382652977731</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.0002723863734915993</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.001379752971443854</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.0008043412157748524</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.0005787609506627193</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.0005</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>100</v>
+      </c>
+      <c r="E12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.0003760104970333195</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.0002781633643584706</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.001434790917765371</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.0008047217122246924</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.0005787783127690765</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>100</v>
+      </c>
+      <c r="E13" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.0003775930816340493</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.0002790716995704797</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.001443863116502349</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.0008047660379869249</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.0005787804912883448</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>5e-05</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>100</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>100</v>
+      </c>
+      <c r="E14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.0003787987329399322</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.0002798186080372248</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.00145127224346917</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.0008048060718584332</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.0005787822367345499</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>1e-05</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_8.xlsx
+++ b/Results/rbf_fd_parameter_study_8.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Stencil Nodes" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Center Rings" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Eigenvalue Ratio" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Eigenvector Angle" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3892,4 +3893,600 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.1137114135128784</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.2415674428912381</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.03845197628403531</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.0008001090726650862</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0005785430003536949</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>100</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.0008408304340721984</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.0005669708284530482</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.001054128938197823</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.0004815883537235223</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.0004626453869301972</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.02602114417110564</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.01366872618932473</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.03146030492138841</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.0004122307896641839</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0004486798148184803</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.00020436909811682</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.0002654039236254764</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.0004131135396127473</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.0004814933354349484</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0004625914814776867</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>100</v>
+      </c>
+      <c r="E6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.0004182009467934709</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.0003363376131591185</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.001868819840252789</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.0008000998633794607</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0005785670172972821</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>100</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>16</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.0001302826061626809</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.0001883751703081106</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.0008466722326686827</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.00130647856235889</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0007913025551806104</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>100</v>
+      </c>
+      <c r="E8" t="n">
+        <v>10</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>18</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.0001373643130164914</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.000240797266814757</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.001061038588597182</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.0009746870818656008</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0008447701880871193</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>20</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0003222377220781772</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0005819542065906979</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.001554526905133144</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.001306462502036973</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0007910953797506564</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>100</v>
+      </c>
+      <c r="E10" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H10" t="n">
+        <v>24</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.1137056880449734</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.2415552336634679</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.03845000678243879</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.0008001090808302143</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.0005785430039626124</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_8.xlsx
+++ b/Results/rbf_fd_parameter_study_8.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Length Scale" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1056,4 +1057,930 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.007777904894110657</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.003846240443397531</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.01321354549514717</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.0486982650858348</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.005978485232907934</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.007752401618671655</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.003825570748335004</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.01311983433932423</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.04890571263252344</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.006005157086740229</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.0009048158954381242</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0007845478991284208</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.003973219914783653</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.00162157862308578</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.00114619211392505</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>30</v>
+      </c>
+      <c r="E5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.009172384027508675</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.007563922393657303</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.04341129080103274</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.002435413866333065</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.002051476148716023</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>30</v>
+      </c>
+      <c r="E6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1.544613279790866e-05</v>
+      </c>
+      <c r="L6" t="n">
+        <v>9.755051747722852e-06</v>
+      </c>
+      <c r="M6" t="n">
+        <v>4.869366246507208e-05</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.0002635243911586938</v>
+      </c>
+      <c r="O6" t="n">
+        <v>4.197188011352694e-05</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>30</v>
+      </c>
+      <c r="E7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.813430912374811e-05</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.898039159985543e-05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>9.162980301161816e-05</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.0005007678226198691</v>
+      </c>
+      <c r="O7" t="n">
+        <v>8.053566450562735e-05</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>30</v>
+      </c>
+      <c r="E8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.000147131649777583</v>
+      </c>
+      <c r="L8" t="n">
+        <v>8.534880906588148e-05</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.0006087208857318716</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.0008617630513712635</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0001503082568099237</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.911727128116873e-05</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3.636238982666237e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.0001415825279778436</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.0006317903368249495</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0001704583898223327</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>30</v>
+      </c>
+      <c r="E10" t="n">
+        <v>12</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5.525497785737412e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>6.980595511094484e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.0002196374046790869</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.0009758831792351583</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.0003272394373162871</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>30</v>
+      </c>
+      <c r="E11" t="n">
+        <v>12</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.0002188582632579027</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.0002544620922776963</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.0006875985708817328</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.001071235068182201</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.0007436984788551136</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D12" t="n">
+        <v>30</v>
+      </c>
+      <c r="E12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.0002144325930278544</v>
+      </c>
+      <c r="L12" t="n">
+        <v>4.940167820293746e-05</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.008737691613154082</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.03482809274828284</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.001768786660418733</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" t="n">
+        <v>30</v>
+      </c>
+      <c r="E13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>6.334384039714323e-05</v>
+      </c>
+      <c r="L13" t="n">
+        <v>6.293152679201609e-05</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.001901097279161436</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.08889177607604935</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.005104481705021272</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>100</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n">
+        <v>15</v>
+      </c>
+      <c r="D14" t="n">
+        <v>30</v>
+      </c>
+      <c r="E14" t="n">
+        <v>12</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.001894788113532354</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.0006237183492986875</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.2374208799364033</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.175671472082935</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.1089883766786373</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>100</v>
+      </c>
+      <c r="B15" t="n">
+        <v>100</v>
+      </c>
+      <c r="C15" t="n">
+        <v>20</v>
+      </c>
+      <c r="D15" t="n">
+        <v>30</v>
+      </c>
+      <c r="E15" t="n">
+        <v>12</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H15" t="n">
+        <v>12</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.003128147124474746</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.004260471476487617</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.05966963584144764</v>
+      </c>
+      <c r="N15" t="n">
+        <v>14.8681295118016</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.7413304878361057</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>100</v>
+      </c>
+      <c r="B16" t="n">
+        <v>100</v>
+      </c>
+      <c r="C16" t="n">
+        <v>30</v>
+      </c>
+      <c r="D16" t="n">
+        <v>30</v>
+      </c>
+      <c r="E16" t="n">
+        <v>12</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H16" t="n">
+        <v>12</v>
+      </c>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="b">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.08254050484806336</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.1182750256597431</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.3133510481886213</v>
+      </c>
+      <c r="N16" t="n">
+        <v>24.66768515895185</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.930615269685242</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Inverse Length Scale</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_8.xlsx
+++ b/Results/rbf_fd_parameter_study_8.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Length Scale" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Stencil Nodes" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1983,4 +1984,875 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.1050632650842351</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.01710191964137647</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.1352624922758837</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.00792191185005882</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.002022275075657004</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>25</v>
+      </c>
+      <c r="E3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.0001777894390987835</v>
+      </c>
+      <c r="L3" t="n">
+        <v>7.11797585215662e-05</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.0004171142194751698</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.0007885779506221498</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.0002509133857671765</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>40</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.0002835086759907691</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0003050731675858932</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.001682582527499314</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.0004948590816767257</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0003417774018312593</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>50</v>
+      </c>
+      <c r="E5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.0002445697994196729</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.0002363596601157739</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.0005279105431988086</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.0008497097351800284</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0006674623953845563</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>65</v>
+      </c>
+      <c r="E6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.0007685252042734211</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.0004547654040889007</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.003142739040650259</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.0009583862005247091</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0009722914482955366</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>75</v>
+      </c>
+      <c r="E7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.002832249818915617</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.001746605438651624</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.009864830239326928</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.001279243679386152</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.001276636418064235</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>85</v>
+      </c>
+      <c r="E8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.0004384896557824352</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.0005848788642918038</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.00139023372808998</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.001379241690192191</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.001686280178899425</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0003037884580966019</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0002147060583145756</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.003191066556170407</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.0006641410300217858</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0001681167812749773</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>115</v>
+      </c>
+      <c r="E10" t="n">
+        <v>12</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.0005581682905231147</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.0002591100882581255</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.002364263008939466</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.0001728474988361421</v>
+      </c>
+      <c r="O10" t="n">
+        <v>5.004340307247643e-05</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>130</v>
+      </c>
+      <c r="E11" t="n">
+        <v>12</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>8.166368660909497e-05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>5.822264203205707e-05</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.0002954646589099913</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.0002492538189122731</v>
+      </c>
+      <c r="O11" t="n">
+        <v>6.515401484642719e-05</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>150</v>
+      </c>
+      <c r="E12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>6.082421379935749e-05</v>
+      </c>
+      <c r="L12" t="n">
+        <v>3.875153618160561e-05</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.0001768542471415026</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.0002456553211317587</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.000107647248894915</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>175</v>
+      </c>
+      <c r="E13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>8.838296129446266e-05</v>
+      </c>
+      <c r="L13" t="n">
+        <v>6.489269837676075e-05</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.0002741212387390921</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.0001940766445179668</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.000109342339370183</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>100</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>200</v>
+      </c>
+      <c r="E14" t="n">
+        <v>12</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.0005121280261953351</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.0003316786656365431</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.001449968345655298</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.0002823337007756666</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.0001738673107928255</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>100</v>
+      </c>
+      <c r="B15" t="n">
+        <v>100</v>
+      </c>
+      <c r="C15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>250</v>
+      </c>
+      <c r="E15" t="n">
+        <v>12</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H15" t="n">
+        <v>12</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.0007794751978307894</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.0004188699244134988</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.001437896479029551</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.0003797727023798845</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.0002721843567561567</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>250</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_8.xlsx
+++ b/Results/rbf_fd_parameter_study_8.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Grid Size" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Length Scale" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Stencil Nodes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Center Rings" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2855,4 +2856,655 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>6.008669134359276e-05</v>
+      </c>
+      <c r="L2" t="n">
+        <v>7.176076590240446e-05</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.0001743567859577754</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.0005410616142075399</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0002413582037583164</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>6.056819313699134e-05</v>
+      </c>
+      <c r="L3" t="n">
+        <v>7.192178824593879e-05</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.0001733518554363847</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.0005350117456286019</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.000240694532306167</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>6.060778288720793e-05</v>
+      </c>
+      <c r="L4" t="n">
+        <v>7.187187322622716e-05</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.0001770516654017013</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.0005308678719830546</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0002401645510342136</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>30</v>
+      </c>
+      <c r="E5" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>6.092159122115923e-05</v>
+      </c>
+      <c r="L5" t="n">
+        <v>7.194178197400566e-05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.0001756184620061214</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.000529066614415282</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0002398939726306964</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>30</v>
+      </c>
+      <c r="E6" t="n">
+        <v>9</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6.096896826362452e-05</v>
+      </c>
+      <c r="L6" t="n">
+        <v>7.197700987869729e-05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.0001747284492369703</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.000528199436191636</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0002398433820810426</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>30</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>9.572126032188743e-05</v>
+      </c>
+      <c r="L7" t="n">
+        <v>7.895376757974232e-05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.0004069263541692506</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.0009769185921273903</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0003277361198033744</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>30</v>
+      </c>
+      <c r="E8" t="n">
+        <v>11</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>8.881421550627079e-05</v>
+      </c>
+      <c r="L8" t="n">
+        <v>7.744775076445435e-05</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.0003493690063691659</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.000976357944739922</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0003280698966384151</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>5.525497785737412e-05</v>
+      </c>
+      <c r="L9" t="n">
+        <v>6.980595511094484e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.0002196374046790869</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.0009758831792351583</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0003272394373162871</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>30</v>
+      </c>
+      <c r="E10" t="n">
+        <v>13</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>6.774341092459103e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>7.146378978481885e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.0001946029008656318</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.0008894328226201054</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.000324822426716602</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>30</v>
+      </c>
+      <c r="E11" t="n">
+        <v>14</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>8.148799957814481e-05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>7.530675370761875e-05</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.0002256583276666244</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.0009560852305290398</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.0003254743398435532</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_8.xlsx
+++ b/Results/rbf_fd_parameter_study_8.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Length Scale" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Stencil Nodes" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Center Rings" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Eigenvalue Ratio" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3507,4 +3508,820 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>10</v>
+      </c>
+      <c r="H2" t="n">
+        <v>12</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.0003616287788626968</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.0006522872014558316</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.0005930069242507057</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.00114184453529679</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0003095860877751879</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.0001267718198169936</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.0002308904027883459</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.0003986137844128178</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.001120256115733003</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.0002918305362280818</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>6.828317846369603e-05</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0001067626715933071</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.0002451678738147445</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.001025266945496748</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0002508426532335889</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>30</v>
+      </c>
+      <c r="E5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>5.85223841672562e-05</v>
+      </c>
+      <c r="L5" t="n">
+        <v>9.890149879904266e-05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.0002192583799868227</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.0009777726627375554</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0002604428788536846</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>30</v>
+      </c>
+      <c r="E6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4.783062788500569e-05</v>
+      </c>
+      <c r="L6" t="n">
+        <v>7.71239242869418e-05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.0002144585998793049</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.0009086898144456525</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0003055061795607249</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>30</v>
+      </c>
+      <c r="E7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H7" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>5.743643856933484e-05</v>
+      </c>
+      <c r="L7" t="n">
+        <v>7.270534600468606e-05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.0002982733510827529</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.0009247674803998728</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0003161948050059364</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>30</v>
+      </c>
+      <c r="E8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H8" t="n">
+        <v>12</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.0003095057205766213</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.0001386462510136432</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.002620061590309797</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.0009699786352145735</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.000325940490281853</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>5.525497785737412e-05</v>
+      </c>
+      <c r="L9" t="n">
+        <v>6.980595511094484e-05</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.0002196374046790869</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.0009758831792351583</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0003272394373162871</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>30</v>
+      </c>
+      <c r="E10" t="n">
+        <v>12</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.0001058754226077989</v>
+      </c>
+      <c r="L10" t="n">
+        <v>7.701452428461948e-05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.000496516131065682</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.0009806491192043442</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.0003282920859404347</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>100</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>30</v>
+      </c>
+      <c r="E11" t="n">
+        <v>12</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>9.386449324768984e-05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>7.369840926989957e-05</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.0004047275819026303</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.0009812474230481091</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.0003284245876910534</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.0005</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>30</v>
+      </c>
+      <c r="E12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="H12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>9.571249370959935e-05</v>
+      </c>
+      <c r="L12" t="n">
+        <v>7.36634461888794e-05</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.0004056755520245062</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.0009817267025189124</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.0003285305981396998</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>100</v>
+      </c>
+      <c r="B13" t="n">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>30</v>
+      </c>
+      <c r="E13" t="n">
+        <v>12</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>5e-05</v>
+      </c>
+      <c r="H13" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>9.607771795025285e-05</v>
+      </c>
+      <c r="L13" t="n">
+        <v>7.379960970620962e-05</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.0004099319814482754</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.0009817866625680101</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.0003285438625561475</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>5e-05</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>100</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>30</v>
+      </c>
+      <c r="E14" t="n">
+        <v>12</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="H14" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>9.643497544356437e-05</v>
+      </c>
+      <c r="L14" t="n">
+        <v>7.393117763315271e-05</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.0004140172659446772</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.000981834582744175</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.0003285545105385204</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>eig_2</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>1e-05</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Results/rbf_fd_parameter_study_8.xlsx
+++ b/Results/rbf_fd_parameter_study_8.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Stencil Nodes" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Center Rings" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Eigenvalue Ratio" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Eigenvector Angle" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4324,4 +4325,600 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Nx</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ny</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>num_stencil_nodes</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>num_rings</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eigenvalue 1</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>eigenvalue 2</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>radian = r/24</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>augmentation</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sparse</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>u_exact - u max_error_rel</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>u_exact - u l2_error_rel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>energy_error_rel</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F max_residual_rel</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Lu_exact - F l2_residual_rel</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>varied_param</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>varied_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2" t="n">
+        <v>12</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.007535679360162343</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.01803805804419991</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.003052260708736629</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.001166332871365945</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0003305340477556942</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>100</v>
+      </c>
+      <c r="B3" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.0004243668533194617</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.0005925996195937711</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.0008374149690531904</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.0007069335349264783</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.0002042724989789685</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>30</v>
+      </c>
+      <c r="E4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>6</v>
+      </c>
+      <c r="I4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.0003110359124315162</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.0002907055462578193</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.0005863185309700203</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.0006279968963014578</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0001815897100507824</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>100</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>30</v>
+      </c>
+      <c r="E5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>6.761022816584144e-05</v>
+      </c>
+      <c r="L5" t="n">
+        <v>8.986356545869487e-05</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.0002083571124906453</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.0006169567917537038</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.0002031023076098384</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>30</v>
+      </c>
+      <c r="E6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>5.525497785737412e-05</v>
+      </c>
+      <c r="L6" t="n">
+        <v>6.980595511094484e-05</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.0002196374046790869</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.0009758831792351583</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0003272394373162871</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>30</v>
+      </c>
+      <c r="E7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H7" t="n">
+        <v>16</v>
+      </c>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>7.560794700002024e-05</v>
+      </c>
+      <c r="L7" t="n">
+        <v>9.325261432734586e-05</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.0005611503492183651</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.002180022366068151</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0004180374745849256</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>30</v>
+      </c>
+      <c r="E8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H8" t="n">
+        <v>18</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>9.425564775711121e-05</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.0001348844357352375</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.0007302700122662484</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.002891306032243164</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0004189134268007525</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>100</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>30</v>
+      </c>
+      <c r="E9" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H9" t="n">
+        <v>20</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0002589426157278761</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0002130864920656509</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.001804050887414634</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.002506413184417021</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0004220128794549585</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>30</v>
+      </c>
+      <c r="E10" t="n">
+        <v>12</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H10" t="n">
+        <v>24</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.007535669052291766</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.01803803748720403</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.003052258097693646</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.001166332865018876</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.0003305340495362953</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>rad24</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>